--- a/data/trans_dic/P19C08-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C08-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por selladores, aplicación de fluor</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por selladores, aplicación de fluor (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,94</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,02</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,66</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,37</t>
+          <t>0,25; 2,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,91</t>
+          <t>0,2; 1,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,17</t>
+          <t>0,0; 0,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,07</t>
+          <t>0,0; 0,08</t>
         </is>
       </c>
     </row>
@@ -997,42 +997,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,26</t>
+          <t>0,34; 3,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,41</t>
+          <t>0,29; 2,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,93</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,11</t>
+          <t>0,46; 2,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,54</t>
+          <t>0,15; 1,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,45</t>
+          <t>0,0; 0,51</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 2,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,96</t>
+          <t>0,0; 4,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,99</t>
+          <t>0,13; 2,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,22</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1277,37 +1277,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,35</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,73</t>
+          <t>0,0; 3,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,18</t>
+          <t>0,26; 2,12</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,43</t>
+          <t>0,25; 1,48</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,62</t>
+          <t>0,71; 5,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,66</t>
+          <t>0,54; 2,97</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
     </row>
@@ -1562,57 +1562,57 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,27</t>
+          <t>0,17; 2,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,25</t>
+          <t>0,42; 3,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,54</t>
+          <t>0,17; 1,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,06</t>
+          <t>0,21; 2,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,55</t>
+          <t>0,21; 1,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,9</t>
+          <t>0,09; 0,92</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,16</t>
+          <t>0,17; 1,24</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,08</t>
+          <t>0,1; 1,12</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,87</t>
+          <t>0,43; 1,87</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,72</t>
+          <t>0,17; 1,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,53</t>
+          <t>0,16; 1,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,26</t>
+          <t>0,14; 1,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,24</t>
+          <t>0,31; 2,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,3</t>
+          <t>0,14; 1,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,36</t>
+          <t>0,26; 1,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,6</t>
+          <t>0,4; 1,54</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,01</t>
+          <t>0,22; 1,06</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,06</t>
+          <t>0,3; 1,08</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,64</t>
+          <t>0,15; 0,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,99</t>
+          <t>0,36; 1,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,36</t>
+          <t>0,04; 0,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,85</t>
+          <t>0,25; 0,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,89</t>
+          <t>0,29; 0,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,96</t>
+          <t>0,37; 0,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,43</t>
+          <t>0,08; 0,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,61</t>
+          <t>0,23; 0,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,66</t>
+          <t>0,29; 0,68</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,85</t>
+          <t>0,43; 0,86</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,35</t>
+          <t>0,08; 0,34</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,61</t>
+          <t>0,28; 0,63</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por selladores, aplicación de fluor</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por selladores, aplicación de fluor (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5792</t>
+          <t>0; 6767</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5935</t>
+          <t>0; 6606</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 7214</t>
+          <t>0; 7151</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1844</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 8086</t>
+          <t>0; 6984</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6622</t>
+          <t>0; 6156</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1970</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1038</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>978; 9297</t>
+          <t>979; 9916</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>993; 9522</t>
+          <t>989; 8774</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 7266</t>
+          <t>0; 7202</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 1341</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2043</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2037</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5812</t>
+          <t>0; 6583</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2616</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1929</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6161</t>
+          <t>0; 7016</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2024</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 875</t>
+          <t>0; 943</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1985</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 6077</t>
+          <t>0; 7038</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5748</t>
+          <t>0; 6510</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 743</t>
+          <t>0; 834</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1957</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>989; 9584</t>
+          <t>1002; 9839</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4580</t>
+          <t>0; 4574</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1671</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5722</t>
+          <t>0; 6138</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>969; 7916</t>
+          <t>938; 7652</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 8122</t>
+          <t>0; 8303</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3130</t>
+          <t>0; 3194</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5765</t>
+          <t>0; 5789</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2904; 13107</t>
+          <t>2880; 13817</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>917; 9188</t>
+          <t>906; 8786</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 2861</t>
+          <t>0; 3220</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4649</t>
+          <t>0; 5760</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 12402</t>
+          <t>0; 14556</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2011</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2060</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1861</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5425</t>
+          <t>0; 4716</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2067</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 1528</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5163</t>
+          <t>0; 4775</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>865; 13067</t>
+          <t>885; 16068</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 2043</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 1704</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5696</t>
+          <t>0; 4716</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2082</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1921</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3682</t>
+          <t>0; 3537</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6495</t>
+          <t>0; 5602</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1977</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 1824</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>433; 4002</t>
+          <t>435; 4010</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>914; 7509</t>
+          <t>904; 7311</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 2034</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 1875</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>922; 5310</t>
+          <t>918; 5486</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1942</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4777</t>
+          <t>0; 5204</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1941</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 7291</t>
+          <t>0; 5997</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6138</t>
+          <t>0; 5948</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2069; 14885</t>
+          <t>1888; 13775</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 1968</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3454</t>
+          <t>0; 3323</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 6652</t>
+          <t>0; 5558</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2828; 13694</t>
+          <t>2802; 15293</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 1960</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 9943</t>
+          <t>0; 7903</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4476</t>
+          <t>0; 4474</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>958; 13066</t>
+          <t>957; 12218</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 2194</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2164; 19498</t>
+          <t>2492; 20963</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>928; 8289</t>
+          <t>926; 8222</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 5744</t>
+          <t>0; 6679</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 10029</t>
+          <t>1040; 10554</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1659; 12819</t>
+          <t>1705; 13037</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>979; 9059</t>
+          <t>937; 9209</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1998; 13951</t>
+          <t>1986; 14919</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>966; 10030</t>
+          <t>969; 10444</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5713; 26747</t>
+          <t>6087; 26671</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>960; 9030</t>
+          <t>919; 9083</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1095; 9707</t>
+          <t>1039; 10102</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 1992</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1451; 11404</t>
+          <t>1288; 11487</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2024; 13256</t>
+          <t>1857; 12996</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>967; 9164</t>
+          <t>964; 8710</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 2087</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2222; 9604</t>
+          <t>1834; 10129</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4658; 17913</t>
+          <t>4469; 17248</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2986; 13505</t>
+          <t>2977; 14115</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 2042</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4413; 17032</t>
+          <t>4757; 17473</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>3726; 15823</t>
+          <t>3733; 14941</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9985; 28863</t>
+          <t>10441; 29281</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>915; 9708</t>
+          <t>1038; 10544</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7900; 28637</t>
+          <t>8224; 27953</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7794; 24415</t>
+          <t>7936; 24589</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11232; 30227</t>
+          <t>11582; 29405</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2128; 12298</t>
+          <t>2214; 13015</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>7857; 21978</t>
+          <t>8204; 22048</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>14889; 34083</t>
+          <t>15066; 35260</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>25791; 51555</t>
+          <t>25996; 51859</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4368; 19251</t>
+          <t>4256; 18797</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>19151; 42190</t>
+          <t>19700; 43624</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C08-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C08-Provincia-trans_dic.xlsx
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,92</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>0,0; 3,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,52</t>
+          <t>0,25; 2,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,76</t>
+          <t>0,2; 1,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,08%</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,19</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,08</t>
+          <t>0,0; 0,42</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,35</t>
+          <t>0,33; 3,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1017,42 +1017,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,33</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,22</t>
+          <t>0,47; 2,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,47</t>
+          <t>0,15; 1,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,51</t>
+          <t>0,0; 0,52</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,65</t>
+          <t>0,0; 4,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,45</t>
+          <t>0,13; 2,02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,22</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,98</t>
+          <t>0,2; 1,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,12</t>
+          <t>0,26; 2,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,48</t>
+          <t>0,27; 1,47</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,17 +1432,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,2</t>
+          <t>0,78; 5,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1452,17 +1452,17 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,97</t>
+          <t>0,4; 2,82</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,12</t>
+          <t>0,18; 2,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1572,47 +1572,47 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,5</t>
+          <t>0,57; 3,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,52</t>
+          <t>0,17; 1,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,17</t>
+          <t>0,2; 2,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,57</t>
+          <t>0,41; 1,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,92</t>
+          <t>0,1; 0,91</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,24</t>
+          <t>0,17; 1,27</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,12</t>
+          <t>0,1; 1,1</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,87</t>
+          <t>0,61; 2,19</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,73</t>
+          <t>0,17; 1,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,59</t>
+          <t>0,16; 1,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1712,17 +1712,17 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,26</t>
+          <t>0,28; 1,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,19</t>
+          <t>0,31; 2,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,24</t>
+          <t>0,14; 1,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1732,17 +1732,17 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,44</t>
+          <t>0,27; 1,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,54</t>
+          <t>0,42; 1,55</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,06</t>
+          <t>0,23; 1,07</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,08</t>
+          <t>0,36; 1,19</t>
         </is>
       </c>
     </row>
@@ -1784,34 +1784,34 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0,61%</t>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,61</t>
+          <t>0,19; 0,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,0</t>
+          <t>0,37; 1,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1852,27 +1852,27 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,83</t>
+          <t>0,3; 0,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,9</t>
+          <t>0,33; 0,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,94</t>
+          <t>0,37; 0,93</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,45</t>
+          <t>0,08; 0,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,62</t>
+          <t>0,29; 0,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,86</t>
+          <t>0,42; 0,86</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,63</t>
+          <t>0,34; 0,72</t>
         </is>
       </c>
     </row>
@@ -2209,17 +2209,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6767</t>
+          <t>0; 6864</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6606</t>
+          <t>0; 5790</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 7151</t>
+          <t>0; 7312</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6984</t>
+          <t>0; 7260</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6156</t>
+          <t>0; 6607</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -2249,17 +2249,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>979; 9916</t>
+          <t>987; 9849</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>989; 8774</t>
+          <t>1002; 9750</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 7202</t>
+          <t>0; 7215</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>873</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>873</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6583</t>
+          <t>0; 6240</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 7016</t>
+          <t>0; 6737</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 943</t>
+          <t>0; 4485</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2462,17 +2462,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 7038</t>
+          <t>0; 6888</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 6510</t>
+          <t>0; 5774</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 834</t>
+          <t>0; 4449</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>572</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>572</t>
         </is>
       </c>
     </row>
@@ -2630,12 +2630,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1002; 9839</t>
+          <t>959; 8892</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4574</t>
+          <t>0; 4610</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2645,42 +2645,42 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6138</t>
+          <t>0; 5615</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>938; 7652</t>
+          <t>0; 7858</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 8303</t>
+          <t>0; 8292</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3194</t>
+          <t>0; 2894</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5789</t>
+          <t>0; 5311</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2880; 13817</t>
+          <t>2924; 13982</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>906; 8786</t>
+          <t>908; 9283</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3220</t>
+          <t>0; 3330</t>
         </is>
       </c>
     </row>
@@ -2833,12 +2833,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5760</t>
+          <t>0; 4832</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 14556</t>
+          <t>0; 13096</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4716</t>
+          <t>0; 4175</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4775</t>
+          <t>0; 4776</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>885; 16068</t>
+          <t>869; 13258</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>2843</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4716</t>
+          <t>0; 4827</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3537</t>
+          <t>0; 4358</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5602</t>
+          <t>0; 6470</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>435; 4010</t>
+          <t>450; 4155</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>904; 7311</t>
+          <t>900; 7474</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>918; 5486</t>
+          <t>1122; 6027</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>637</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>1937</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5204</t>
+          <t>0; 5132</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3264,17 +3264,17 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 5997</t>
+          <t>0; 6035</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5948</t>
+          <t>0; 7092</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1888; 13775</t>
+          <t>2061; 13862</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3284,17 +3284,17 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3323</t>
+          <t>0; 3187</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 5558</t>
+          <t>0; 5749</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2802; 15293</t>
+          <t>2065; 14531</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 7903</t>
+          <t>0; 9982</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7426</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>13169</t>
+          <t>16805</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4474</t>
+          <t>0; 3934</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>957; 12218</t>
+          <t>1041; 12166</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3472,47 +3472,47 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2492; 20963</t>
+          <t>3949; 26706</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>926; 8222</t>
+          <t>926; 8281</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 6679</t>
+          <t>0; 5804</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1040; 10554</t>
+          <t>970; 10564</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1705; 13037</t>
+          <t>3048; 13533</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>937; 9209</t>
+          <t>974; 9161</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1986; 14919</t>
+          <t>2005; 15294</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>969; 10444</t>
+          <t>970; 10230</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6087; 26671</t>
+          <t>8814; 31586</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>11038</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>919; 9083</t>
+          <t>912; 9138</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1039; 10102</t>
+          <t>1005; 9812</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3680,17 +3680,17 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1288; 11487</t>
+          <t>2165; 11759</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1857; 12996</t>
+          <t>1830; 12683</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>964; 8710</t>
+          <t>963; 8766</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3700,17 +3700,17 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1834; 10129</t>
+          <t>2176; 10900</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4469; 17248</t>
+          <t>4667; 17327</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2977; 14115</t>
+          <t>3060; 14246</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4757; 17473</t>
+          <t>5705; 18750</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14985</t>
+          <t>17992</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>16076</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>28514</t>
+          <t>34067</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>3733; 14941</t>
+          <t>4592; 16673</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>10441; 29281</t>
+          <t>10838; 29661</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1038; 10544</t>
+          <t>1024; 10562</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8224; 27953</t>
+          <t>10283; 31836</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7936; 24589</t>
+          <t>8932; 23902</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11582; 29405</t>
+          <t>11713; 29348</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2214; 13015</t>
+          <t>2218; 14876</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>8204; 22048</t>
+          <t>10417; 25346</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>15066; 35260</t>
+          <t>15000; 35213</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>25996; 51859</t>
+          <t>25516; 51921</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4256; 18797</t>
+          <t>4390; 18688</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>19700; 43624</t>
+          <t>23977; 50449</t>
         </is>
       </c>
     </row>
